--- a/Pipeline5App/assets/ButtonsLayout.xlsx
+++ b/Pipeline5App/assets/ButtonsLayout.xlsx
@@ -1061,7 +1061,7 @@
       </c>
       <c r="N8" s="21" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="P8" s="21" t="inlineStr">
@@ -1106,9 +1106,9 @@
           <t>530  Open IO Tags</t>
         </is>
       </c>
-      <c r="N9" s="22" t="inlineStr">
-        <is>
-          <t>630  Open Diag Data Folder</t>
+      <c r="N9" s="19" t="inlineStr">
+        <is>
+          <t>650  Generate Web Application</t>
         </is>
       </c>
       <c r="P9" s="22" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="N11" s="22" t="inlineStr">
         <is>
-          <t>640  Open Diag Config .csv Folder</t>
+          <t>630  Open Diag Data Folder</t>
         </is>
       </c>
       <c r="R11" s="20" t="inlineStr">
@@ -1202,6 +1202,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="N12" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="R12" s="21" t="inlineStr">
         <is>
           <t>—</t>
@@ -1219,6 +1224,11 @@
           <t>245  Risky Index Fill (review)</t>
         </is>
       </c>
+      <c r="N13" s="22" t="inlineStr">
+        <is>
+          <t>640  Open Diag Config .csv Folder</t>
+        </is>
+      </c>
       <c r="R13" s="22" t="inlineStr">
         <is>
           <t>850  Open Generated Blocks Folder</t>
@@ -1236,6 +1246,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="N14" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="60" customHeight="1">
       <c r="D15" s="20" t="inlineStr">
@@ -1246,6 +1261,11 @@
       <c r="F15" s="22" t="inlineStr">
         <is>
           <t>250  Open I/O List</t>
+        </is>
+      </c>
+      <c r="N15" s="22" t="inlineStr">
+        <is>
+          <t>660  Open Web Application Folder</t>
         </is>
       </c>
     </row>
